--- a/results/reliability_eval/reliability_eval_09-03-1/Llama-3-8B_P101_neg1_sample_15_tokens_0.1_temp_direct_answer_scores_09-03-1.xlsx
+++ b/results/reliability_eval/reliability_eval_09-03-1/Llama-3-8B_P101_neg1_sample_15_tokens_0.1_temp_direct_answer_scores_09-03-1.xlsx
@@ -477,31 +477,31 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.5122759596469454</v>
+        <v>0.5262831958183775</v>
       </c>
       <c r="B2" t="n">
-        <v>0.2478499688916971</v>
+        <v>0.1541333693668091</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5122759596469454</v>
+        <v>0.5262831958183772</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2478499688916971</v>
+        <v>0.1541333693668091</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4886362120775321</v>
+        <v>0.472996518145629</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2389801701314956</v>
+        <v>0.1403024979185589</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9952076786574728</v>
+        <v>0.9950979747222068</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9827497898003604</v>
+        <v>0.9671630813436749</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2375</v>
+        <v>0.1449712643678161</v>
       </c>
     </row>
   </sheetData>
